--- a/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721905B2-40A8-45C4-9C9E-FCBAE26CDE1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A8FD7E-7AD5-4836-887C-BAAC3A5CD2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13890" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,6 @@
     <t>variable</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t xml:space="preserve">ID </t>
   </si>
   <si>
@@ -61,24 +58,15 @@
     <t>Weiblich</t>
   </si>
   <si>
-    <t xml:space="preserve"> Geschlecht </t>
-  </si>
-  <si>
     <t>age</t>
   </si>
   <si>
     <t>decimal</t>
   </si>
   <si>
-    <t xml:space="preserve"> Alter (in vollendeten Lebensjahren) </t>
-  </si>
-  <si>
     <t>RCstatD</t>
   </si>
   <si>
-    <t xml:space="preserve"> Rauchen </t>
-  </si>
-  <si>
     <t>Ja, täglich</t>
   </si>
   <si>
@@ -178,9 +166,6 @@
     <t>Hypertonie (12-Mon-Prävalenz)</t>
   </si>
   <si>
-    <t xml:space="preserve"> Diabetes (12-Mon-Prävalenz) </t>
-  </si>
-  <si>
     <t>Ja</t>
   </si>
   <si>
@@ -235,10 +220,6 @@
     <t>Regelblutung in den letzten 12 Monaten</t>
   </si>
   <si>
-    <t xml:space="preserve">1
-</t>
-  </si>
-  <si>
     <t>RCexC_a</t>
   </si>
   <si>
@@ -267,13 +248,31 @@
   </si>
   <si>
     <t>Degree from a university</t>
+  </si>
+  <si>
+    <t>ID0339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diabetes (12-Mon-Prävalenz) </t>
+  </si>
+  <si>
+    <t>missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauchen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geschlecht </t>
+  </si>
+  <si>
+    <t>Alter (in vollendeten Lebensjahren)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,10 +308,18 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -335,36 +342,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -380,9 +397,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -420,9 +437,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -455,26 +472,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -507,26 +507,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -701,299 +684,324 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="56.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11"/>
+      <c r="B6" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="C14" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="C19" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="D19" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="C22" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
+      <c r="D22" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C23" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
+      <c r="D23" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C25" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D25" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12"/>
+      <c r="B26" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
+      <c r="C26" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>13</v>
+      <c r="D26" s="14" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1004,14 +1012,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1021,379 +1029,484 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>61</v>
+        <v>9</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>61</v>
+      <c r="C4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>61</v>
+        <v>68</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>61</v>
+      <c r="C6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>61</v>
+      <c r="C7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>61</v>
+      <c r="C8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>61</v>
+      <c r="C9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>15</v>
+      <c r="C10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="B15">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>40</v>
+        <v>15</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>40</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>40</v>
+        <v>33</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B20">
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>55</v>
+        <v>35</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>55</v>
+        <v>46</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
         <v>47</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>53</v>
+        <v>46</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30">
+        <v>47</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="7">
         <v>1</v>
       </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31">
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="7">
         <v>2</v>
       </c>
-      <c r="C31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>58</v>
+      <c r="C31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>58</v>
+        <v>46</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>65</v>
+        <v>47</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="6">
+        <v>1</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
-      <c r="C35" t="s">
-        <v>67</v>
+      <c r="C35" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A8FD7E-7AD5-4836-887C-BAAC3A5CD2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DDC9A8-BAD1-4342-9AD1-455DEBB195C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="81">
   <si>
     <t>index</t>
   </si>
@@ -205,18 +205,6 @@
     <t>Age at end of follow-up [years]</t>
   </si>
   <si>
-    <t>MIstaat_m1</t>
-  </si>
-  <si>
-    <t>MIstaat_m2</t>
-  </si>
-  <si>
-    <t>Staatsangehörigkeit: Deutsch</t>
-  </si>
-  <si>
-    <t>Staatsangehörigkeit: Andere</t>
-  </si>
-  <si>
     <t>Regelblutung in den letzten 12 Monaten</t>
   </si>
   <si>
@@ -229,27 +217,6 @@
     <t>RCz4C</t>
   </si>
   <si>
-    <t>Primary School Level</t>
-  </si>
-  <si>
-    <t>Realschule, Mittlere Reife</t>
-  </si>
-  <si>
-    <t>Vocational training in the dual system</t>
-  </si>
-  <si>
-    <t>Entrance qualification for a university of applied sciences and Abitur</t>
-  </si>
-  <si>
-    <t>Post-secondary non-tertiary education</t>
-  </si>
-  <si>
-    <t>Master craftsman, technician, health-care schools, administrative college</t>
-  </si>
-  <si>
-    <t>Degree from a university</t>
-  </si>
-  <si>
     <t>ID0339</t>
   </si>
   <si>
@@ -266,6 +233,42 @@
   </si>
   <si>
     <t>Alter (in vollendeten Lebensjahren)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>5B</t>
+  </si>
+  <si>
+    <t>5A</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>MIausl</t>
+  </si>
+  <si>
+    <t>Ausländ. Staatsangehörigkeit (lt. Einwohnermeldeamt)</t>
+  </si>
+  <si>
+    <t>Ausländer</t>
+  </si>
+  <si>
+    <t>Kein Ausländer</t>
   </si>
 </sst>
 </file>
@@ -308,18 +311,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -342,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -353,11 +355,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -373,15 +371,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -397,9 +393,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -437,9 +433,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -472,9 +468,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -507,9 +520,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -683,324 +713,311 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="56.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="11"/>
-      <c r="B14" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
-      <c r="B20" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="14" t="s">
+      <c r="D25" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1012,8 +1029,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.85546875" bestFit="1" customWidth="1"/>
@@ -1030,7 +1047,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1069,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -1082,8 +1099,8 @@
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>68</v>
+      <c r="C5" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -1096,8 +1113,8 @@
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>69</v>
+      <c r="C6" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -1111,7 +1128,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -1125,7 +1142,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1138,8 +1155,8 @@
       <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>72</v>
+      <c r="C9" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -1152,92 +1169,92 @@
       <c r="B10">
         <v>7</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>73</v>
+      <c r="C10" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>2</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>4</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>15</v>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -1248,10 +1265,10 @@
         <v>36</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -1262,10 +1279,10 @@
         <v>36</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -1276,10 +1293,10 @@
         <v>36</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -1290,10 +1307,10 @@
         <v>36</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -1304,10 +1321,10 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -1315,13 +1332,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -1332,80 +1349,80 @@
         <v>50</v>
       </c>
       <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24">
         <v>2</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>47</v>
       </c>
-      <c r="D23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>1</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>46</v>
       </c>
-      <c r="D24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>2</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>47</v>
       </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>1</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>46</v>
       </c>
-      <c r="D26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>2</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>47</v>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>46</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -1416,10 +1433,10 @@
         <v>48</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -1427,12 +1444,12 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="7">
-        <v>1</v>
-      </c>
-      <c r="C30" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
         <v>47</v>
       </c>
       <c r="D30" t="b">
@@ -1443,10 +1460,10 @@
       <c r="A31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="7">
-        <v>2</v>
-      </c>
-      <c r="C31" s="7" t="s">
+      <c r="B31" s="13">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D31" t="b">
@@ -1455,13 +1472,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="D32" t="b">
         <v>0</v>
@@ -1472,40 +1489,54 @@
         <v>53</v>
       </c>
       <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34">
         <v>2</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>47</v>
       </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="6">
-        <v>1</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="D34" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>60</v>
+      <c r="A35" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>46</v>
+      <c r="C35" t="s">
+        <v>79</v>
       </c>
       <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="b">
         <v>0</v>
       </c>
     </row>

--- a/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DDC9A8-BAD1-4342-9AD1-455DEBB195C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0752384-88A2-4847-9D20-CE8D4D9D9BC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
   <si>
     <t>index</t>
   </si>
@@ -269,13 +269,25 @@
   </si>
   <si>
     <t>Kein Ausländer</t>
+  </si>
+  <si>
+    <t>Gesamt</t>
+  </si>
+  <si>
+    <t>Filterbed. fehlend (lebt nicht im HH)</t>
+  </si>
+  <si>
+    <t>Nicht erhoben (18+ Jahre)</t>
+  </si>
+  <si>
+    <t>Nicht erhoben</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,6 +335,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -344,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -375,6 +394,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,7 +989,7 @@
       <c r="B21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="14" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="10" t="s">
@@ -1029,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -1079,17 +1101,17 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>56</v>
+      <c r="A4" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B4">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="b">
         <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1097,10 +1119,10 @@
         <v>56</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -1111,10 +1133,10 @@
         <v>56</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -1125,10 +1147,10 @@
         <v>56</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -1139,10 +1161,10 @@
         <v>56</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1153,10 +1175,10 @@
         <v>56</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -1167,10 +1189,10 @@
         <v>56</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -1181,55 +1203,55 @@
         <v>56</v>
       </c>
       <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
         <v>8</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13">
+        <v>-96</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>12</v>
+      <c r="A14" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
-        <v>16</v>
+        <v>-97</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1237,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -1251,52 +1273,52 @@
         <v>12</v>
       </c>
       <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C19" t="s">
         <v>15</v>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -1307,10 +1329,10 @@
         <v>36</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -1321,10 +1343,10 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -1335,10 +1357,10 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -1346,13 +1368,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -1360,55 +1382,55 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B24">
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
         <v>2</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C27" t="s">
         <v>47</v>
-      </c>
-      <c r="D24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -1416,55 +1438,55 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B28">
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31">
         <v>2</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C31" t="s">
         <v>47</v>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="13">
-        <v>1</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -1472,13 +1494,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="13">
-        <v>2</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>46</v>
       </c>
       <c r="D32" t="b">
         <v>0</v>
@@ -1486,13 +1508,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
@@ -1500,44 +1522,100 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="13">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="13">
+        <v>2</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B34">
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37">
         <v>2</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C37" t="s">
         <v>47</v>
       </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B35">
+      <c r="B38">
         <v>1</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C38" t="s">
         <v>79</v>
       </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B36">
+      <c r="B39">
         <v>2</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C39" t="s">
         <v>80</v>
       </c>
-      <c r="D36" t="b">
-        <v>0</v>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40">
+        <v>-97</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\use-cases-harmonisation\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0752384-88A2-4847-9D20-CE8D4D9D9BC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46ABAF3E-56DA-4302-A422-B2F8697901CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -399,7 +399,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -415,9 +415,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -455,9 +455,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -490,26 +490,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -542,26 +525,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -736,7 +702,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="56.28515625" style="5" customWidth="1"/>
@@ -789,7 +755,7 @@
         <v>68</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1029,7 +995,7 @@
         <v>58</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1052,7 +1018,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.85546875" bestFit="1" customWidth="1"/>

--- a/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_BGS98_TRACY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46ABAF3E-56DA-4302-A422-B2F8697901CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABED967-4296-4A4E-B7D9-EE9B22F3F3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="84">
   <si>
     <t>index</t>
   </si>
@@ -259,18 +259,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>MIausl</t>
-  </si>
-  <si>
-    <t>Ausländ. Staatsangehörigkeit (lt. Einwohnermeldeamt)</t>
-  </si>
-  <si>
-    <t>Ausländer</t>
-  </si>
-  <si>
-    <t>Kein Ausländer</t>
-  </si>
-  <si>
     <t>Gesamt</t>
   </si>
   <si>
@@ -280,7 +268,16 @@
     <t>Nicht erhoben (18+ Jahre)</t>
   </si>
   <si>
-    <t>Nicht erhoben</t>
+    <t>MIlandB</t>
+  </si>
+  <si>
+    <t>MIstaat_m1</t>
+  </si>
+  <si>
+    <t>Staatsangehörigkeit: Deutsch</t>
+  </si>
+  <si>
+    <t>Geburtsland Deutschland</t>
   </si>
 </sst>
 </file>
@@ -701,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" style="5" customWidth="1"/>
@@ -1000,12 +997,23 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D25" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1017,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -1074,7 +1082,7 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -1200,7 +1208,7 @@
         <v>-96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -1214,7 +1222,7 @@
         <v>-97</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
@@ -1544,13 +1552,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D38" t="b">
         <v>0</v>
@@ -1558,30 +1566,16 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40">
-        <v>-97</v>
-      </c>
-      <c r="C40" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
